--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484760_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484760_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2017</v>
+        <v>6.393</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8056</v>
+        <v>5.2269</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3961</v>
+        <v>1.1661</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4058</v>
+        <v>5.7555</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2648</v>
+        <v>3.7291</v>
       </c>
       <c r="I2" t="n">
-        <v>0.141</v>
+        <v>2.0264</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4564</v>
+        <v>6.1031</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9003</v>
+        <v>4.1204</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4439</v>
+        <v>1.9828</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0506</v>
+        <v>-0.3476</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6354</v>
+        <v>-0.3913</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5849</v>
+        <v>0.0437</v>
       </c>
       <c r="P2" t="n">
-        <v>1.887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R2" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2297</v>
+        <v>0.7131</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>0.0864</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5597</v>
+        <v>0.6267</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3208</v>
+        <v>0.9244</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1303</v>
+        <v>6.2762</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3425</v>
+        <v>5.0703</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7878</v>
+        <v>1.2058</v>
       </c>
       <c r="G3" t="n">
         <v>2.515</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4273</v>
+        <v>1.5731</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9028</v>
+        <v>0.6307</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5244</v>
+        <v>0.9424</v>
       </c>
       <c r="V3" t="n">
         <v>3.6976</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.4594</v>
+        <v>5.3951</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5578</v>
+        <v>2.7926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9015</v>
+        <v>2.6025</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7555</v>
+        <v>2.4058</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7291</v>
+        <v>2.2648</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0264</v>
+        <v>0.141</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1031</v>
+        <v>2.4564</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1204</v>
+        <v>2.9003</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9828</v>
+        <v>-0.4439</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3476</v>
+        <v>-0.0506</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3913</v>
+        <v>-0.6354</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0437</v>
+        <v>0.5849</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7795</v>
+        <v>1.4231</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4173</v>
+        <v>0.657</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3622</v>
+        <v>0.7661</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3018</v>
+        <v>-0.3208</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9244</v>
+        <v>-0.3208</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3229</v>
+        <v>5.2636</v>
       </c>
       <c r="E5" t="n">
-        <v>2.573</v>
+        <v>3.3056</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7499</v>
+        <v>1.9581</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4938</v>
+        <v>2.2215</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8812</v>
+        <v>1.6693</v>
       </c>
       <c r="I5" t="n">
-        <v>2.375</v>
+        <v>0.5523</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1849</v>
+        <v>2.3966</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1723</v>
+        <v>2.2562</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3573</v>
+        <v>0.1404</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3089</v>
+        <v>-0.1751</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2911</v>
+        <v>-0.5869</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0177</v>
+        <v>0.4118</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5084</v>
+        <v>1.0611</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.3244</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6673</v>
+        <v>0.7367</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8868</v>
+        <v>1.2262</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4904</v>
+        <v>1.528</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2137</v>
+        <v>4.0365</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4673</v>
+        <v>2.3395</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7464</v>
+        <v>1.697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2215</v>
+        <v>1.4938</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6693</v>
+        <v>-0.8812</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5523</v>
+        <v>2.375</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3966</v>
+        <v>0.1849</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2562</v>
+        <v>-1.1723</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1404</v>
+        <v>1.3573</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1751</v>
+        <v>1.3089</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5869</v>
+        <v>0.2911</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4118</v>
+        <v>1.0177</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0112</v>
+        <v>1.222</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5139</v>
+        <v>0.6076</v>
       </c>
       <c r="U6" t="n">
-        <v>0.525</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2262</v>
+        <v>1.8868</v>
       </c>
       <c r="W6" t="n">
-        <v>1.528</v>
+        <v>2.4904</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2061</v>
+        <v>3.8765</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4751</v>
+        <v>1.9444</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7309</v>
+        <v>1.9321</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6445</v>
+        <v>2.4464</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.6153</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7445</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8126</v>
+        <v>2.3514</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1942</v>
+        <v>2.2351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.1163</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8318</v>
+        <v>0.095</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2942</v>
+        <v>-0.6198</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1261</v>
+        <v>0.7148</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5426</v>
+        <v>0.3736</v>
       </c>
       <c r="T7" t="n">
-        <v>0.606</v>
+        <v>0.2348</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0634</v>
+        <v>0.1388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.019</v>
+        <v>1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALERO MORANT</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9155</v>
+        <v>3.3874</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4712</v>
+        <v>1.3391</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4444</v>
+        <v>2.0484</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6055</v>
+        <v>2.6445</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1747</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4309</v>
+        <v>1.7445</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6962</v>
+        <v>1.8126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.655</v>
+        <v>1.1942</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0411</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9094</v>
+        <v>0.8318</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5196</v>
+        <v>-0.2942</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3897</v>
+        <v>1.1261</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0082</v>
+        <v>0.724</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4732</v>
+        <v>0.4699</v>
       </c>
       <c r="U8" t="n">
-        <v>0.535</v>
+        <v>0.254</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>0.019</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>J. VALERO MORANT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2819</v>
+        <v>2.5439</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8525</v>
+        <v>1.1789</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4295</v>
+        <v>1.365</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4464</v>
+        <v>1.6055</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6153</v>
+        <v>1.1747</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.4309</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3514</v>
+        <v>0.6962</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2351</v>
+        <v>0.655</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1163</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>0.095</v>
+        <v>0.9094</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6198</v>
+        <v>0.5196</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7148</v>
+        <v>0.3897</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.221</v>
+        <v>0.6365</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8571</v>
+        <v>0.1809</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3638</v>
+        <v>0.4556</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9633</v>
+        <v>1.264</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0664</v>
+        <v>0.1285</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0297</v>
+        <v>1.1355</v>
       </c>
       <c r="G10" t="n">
         <v>0.5865</v>
@@ -1234,13 +1234,13 @@
         <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1881</v>
+        <v>0.4888</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3645</v>
+        <v>0.4703</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7229</v>
+        <v>0.9939</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4378</v>
+        <v>-0.3844</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1607</v>
+        <v>1.3783</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0071</v>
+        <v>-1.2612</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4054</v>
+        <v>1.2357</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3983</v>
+        <v>-2.4969</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2737</v>
+        <v>-1.8391</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2113</v>
+        <v>1.4157</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.485</v>
+        <v>-3.2549</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2809</v>
+        <v>0.5779</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1941</v>
+        <v>-0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0868</v>
+        <v>0.7579</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0741</v>
+        <v>0.123</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.164</v>
+        <v>0.5304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2381</v>
+        <v>-0.4073</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>1.566</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BELLVER VALIENTE</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.9359</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4256</v>
+        <v>-0.1455</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1459</v>
+        <v>1.0813</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2708</v>
+        <v>0.0071</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2293</v>
+        <v>0.4054</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5001</v>
+        <v>-0.3983</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8988</v>
+        <v>-0.2737</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2904</v>
+        <v>0.2113</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.485</v>
       </c>
       <c r="M12" t="n">
-        <v>0.628</v>
+        <v>0.2809</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5196</v>
+        <v>0.1941</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1083</v>
+        <v>0.0868</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8024</v>
+        <v>0.287</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4732</v>
+        <v>0.1283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3292</v>
+        <v>0.1588</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="13">
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>P. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1208</v>
+        <v>0.4809</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1252</v>
+        <v>-0.7179</v>
       </c>
       <c r="F14" t="n">
-        <v>1.246</v>
+        <v>1.1988</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2612</v>
+        <v>-0.2708</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2357</v>
+        <v>0.2293</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.4969</v>
+        <v>-0.5001</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.8391</v>
+        <v>-0.8988</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4157</v>
+        <v>-0.2904</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.2549</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5779</v>
+        <v>0.628</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.18</v>
+        <v>0.5196</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7579</v>
+        <v>0.1083</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7501</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2105</v>
+        <v>0.1809</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5396</v>
+        <v>0.3821</v>
       </c>
       <c r="V14" t="n">
-        <v>1.566</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>40.8758</v>
+        <v>41.4639</v>
       </c>
       <c r="E15" t="n">
-        <v>22.107</v>
+        <v>22.695</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7688</v>
+        <v>18.7689</v>
       </c>
       <c r="G15" t="n">
         <v>20.7666</v>
@@ -1594,7 +1594,7 @@
         <v>16.6537</v>
       </c>
       <c r="I15" t="n">
-        <v>4.113000000000001</v>
+        <v>4.113</v>
       </c>
       <c r="J15" t="n">
         <v>17.2891</v>
@@ -1624,16 +1624,16 @@
         <v>11.322</v>
       </c>
       <c r="S15" t="n">
-        <v>8.6004</v>
+        <v>9.188300000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>3.461799999999999</v>
+        <v>4.049799999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>5.138599999999999</v>
+        <v>5.138600000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>9.621800000000002</v>
+        <v>9.6218</v>
       </c>
       <c r="W15" t="n">
         <v>10.791</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>F. SELLER BERNABE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.26</v>
+        <v>-1.4711</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8028</v>
+        <v>-1.6518</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4572</v>
+        <v>0.1808</v>
       </c>
       <c r="G17" t="n">
-        <v>2.848</v>
+        <v>-1.1207</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5447</v>
+        <v>-0.601</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3033</v>
+        <v>-0.5196</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7733</v>
+        <v>-1.2991</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4231</v>
+        <v>-0.6496</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3502</v>
+        <v>-0.6496</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9253</v>
+        <v>0.1784</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.8784</v>
+        <v>0.0485</v>
       </c>
       <c r="O17" t="n">
-        <v>0.953</v>
+        <v>0.1299</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7871</v>
+        <v>-0.3504</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1605</v>
+        <v>-0.3527</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3734</v>
+        <v>0.0024</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. SELLER BERNABE</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5504</v>
+        <v>-1.694</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6518</v>
+        <v>-0.7054</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1014</v>
+        <v>-0.9887</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1207</v>
+        <v>2.848</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.601</v>
+        <v>0.5447</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5196</v>
+        <v>2.3033</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2991</v>
+        <v>4.7733</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6496</v>
+        <v>3.4231</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6496</v>
+        <v>1.3502</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1784</v>
+        <v>-1.9253</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0485</v>
+        <v>-2.8784</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1299</v>
+        <v>0.953</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4297</v>
+        <v>-1.2211</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3527</v>
+        <v>-1.0631</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.077</v>
+        <v>-0.158</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.805</v>
+        <v>-2.8733</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1961</v>
+        <v>0.0283</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6089</v>
+        <v>-2.9016</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8715</v>
+        <v>-1.8231</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.187</v>
+        <v>-1.62</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6845</v>
+        <v>-0.2031</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2091</v>
+        <v>-0.2832</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7396</v>
+        <v>0.2019</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9487</v>
+        <v>-0.485</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6624</v>
+        <v>-1.5399</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9266</v>
+        <v>-1.8219</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7358</v>
+        <v>0.2819</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8212</v>
+        <v>-0.8051</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.6129</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>-0.1921</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9434</v>
+        <v>-1.566</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0658</v>
+        <v>-3.2946</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1666</v>
+        <v>-0.6832</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8992</v>
+        <v>-2.6113</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8231</v>
+        <v>-2.8715</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.62</v>
+        <v>-0.187</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2031</v>
+        <v>-2.6845</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2832</v>
+        <v>-1.2091</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2019</v>
+        <v>0.7396</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.485</v>
+        <v>-1.9487</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5399</v>
+        <v>-1.6624</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8219</v>
+        <v>-0.9266</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2819</v>
+        <v>-0.7358</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9976</v>
+        <v>0.3317</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8078</v>
+        <v>0.2241</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1898</v>
+        <v>0.1076</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.566</v>
+        <v>-0.9434</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9244</v>
+        <v>0.3018</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2133</v>
+        <v>-3.8905</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6443</v>
+        <v>-2.4779</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.569</v>
+        <v>-1.4126</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1502</v>
+        <v>-2.8942</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0379</v>
+        <v>-2.0801</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1123</v>
+        <v>-0.8141</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.525</v>
+        <v>-0.5463</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6073</v>
+        <v>1.2208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0823</v>
+        <v>-1.7671</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6252</v>
+        <v>-2.3479</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4306</v>
+        <v>-3.301</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1946</v>
+        <v>0.953</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3209</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4403</v>
+        <v>-1.0527</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2323</v>
+        <v>-0.6672</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2081</v>
+        <v>-0.3856</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4267</v>
+        <v>-3.9864</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9681</v>
+        <v>-0.5784</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4586</v>
+        <v>-3.408</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2607</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5625</v>
+        <v>-1.1222</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0582</v>
+        <v>-0.6684</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5043</v>
+        <v>-0.4538</v>
       </c>
       <c r="V22" t="n">
         <v>-1.547</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>M. PEREZ DIEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6084</v>
+        <v>-4.3662</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3804</v>
+        <v>-2.6066</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2279</v>
+        <v>-1.7596</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8942</v>
+        <v>-3.0967</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0801</v>
+        <v>-1.9862</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8141</v>
+        <v>-1.1105</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5463</v>
+        <v>-1.6985</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2208</v>
+        <v>-0.5228</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.7671</v>
+        <v>-1.1757</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3479</v>
+        <v>-1.3982</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.301</v>
+        <v>-1.4634</v>
       </c>
       <c r="O23" t="n">
-        <v>0.953</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7707</v>
+        <v>-0.2885</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5697</v>
+        <v>0.0354</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2009</v>
+        <v>-0.3239</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6226</v>
+        <v>-0.6036</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. PEREZ DIEZ</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6368</v>
+        <v>-4.3965</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5092</v>
+        <v>-2.2744</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1276</v>
+        <v>-2.1221</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0967</v>
+        <v>-1.6695</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9862</v>
+        <v>-3.3949</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1105</v>
+        <v>1.7255</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6985</v>
+        <v>0.1573</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5228</v>
+        <v>-1.1348</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1757</v>
+        <v>1.2921</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3982</v>
+        <v>-1.8267</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4634</v>
+        <v>-2.2601</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.4334</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5591</v>
+        <v>-0.9157</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1328</v>
+        <v>-0.8464</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6919</v>
+        <v>-0.0693</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6036</v>
+        <v>-1.2452</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6036</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0497</v>
+        <v>-4.4791</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9564</v>
+        <v>-2.9366</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0933</v>
+        <v>-1.5425</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6695</v>
+        <v>-2.1502</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3949</v>
+        <v>-2.0379</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7255</v>
+        <v>-0.1123</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1573</v>
+        <v>-0.525</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1348</v>
+        <v>-0.6073</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2921</v>
+        <v>0.0823</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8267</v>
+        <v>-1.6252</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.2601</v>
+        <v>-1.4306</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4334</v>
+        <v>-0.1946</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5661</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.887</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.569</v>
+        <v>-0.7062</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5285</v>
+        <v>-0.5246</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0405</v>
+        <v>-0.1816</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1332</v>
+        <v>-5.1598</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6716</v>
+        <v>-2.1699</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4616</v>
+        <v>-2.9899</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.554</v>
+        <v>-3.4248</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.9567</v>
+        <v>-1.3508</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5974</v>
+        <v>-2.0741</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.3941</v>
+        <v>-1.7938</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.753</v>
+        <v>0.0641</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.641</v>
+        <v>-1.8579</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.16</v>
+        <v>-1.6311</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2036</v>
+        <v>-1.4149</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0437</v>
+        <v>-0.2162</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3339</v>
+        <v>-0.7541</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0058</v>
+        <v>-0.3761</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3397</v>
+        <v>-0.3779</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.3398</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.9054</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3775</v>
+        <v>-5.2162</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.0725</v>
+        <v>-3.9639</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.305</v>
+        <v>-1.2523</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.4248</v>
+        <v>-3.554</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3508</v>
+        <v>-2.9567</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.0741</v>
+        <v>-0.5974</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.7938</v>
+        <v>-2.3941</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0641</v>
+        <v>-1.753</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.8579</v>
+        <v>-0.641</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.6311</v>
+        <v>-1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.4149</v>
+        <v>-1.2036</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.2162</v>
+        <v>0.0437</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.9717</v>
+        <v>-0.417</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2787</v>
+        <v>-0.2865</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.1305</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.547</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-40.8759</v>
+        <v>-39.5768</v>
       </c>
       <c r="E28" t="n">
         <v>-18.7689</v>
       </c>
       <c r="F28" t="n">
-        <v>-22.1069</v>
+        <v>-20.8078</v>
       </c>
       <c r="G28" t="n">
         <v>-20.7665</v>
@@ -2614,7 +2614,7 @@
         <v>-3.4775</v>
       </c>
       <c r="K28" t="n">
-        <v>1.721599999999999</v>
+        <v>1.7216</v>
       </c>
       <c r="L28" t="n">
         <v>-5.199</v>
@@ -2635,16 +2635,16 @@
         <v>-11.322</v>
       </c>
       <c r="R28" t="n">
-        <v>9.435000000000002</v>
+        <v>9.435</v>
       </c>
       <c r="S28" t="n">
-        <v>-8.600399999999999</v>
+        <v>-7.3013</v>
       </c>
       <c r="T28" t="n">
-        <v>-5.1386</v>
+        <v>-5.1384</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.4618</v>
+        <v>-2.1627</v>
       </c>
       <c r="V28" t="n">
         <v>-9.621800000000002</v>
